--- a/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -12186,7 +12186,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 9月14日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 9月16日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -12443,16 +12443,16 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>9</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>10</v>
@@ -12461,7 +12461,7 @@
         <v>8</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.8</v>
@@ -12476,16 +12476,16 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>9</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>12</v>
@@ -12494,7 +12494,7 @@
         <v>11</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>0.9230769230769231</v>
+        <v>1</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>0.9166666666666666</v>
@@ -12509,16 +12509,16 @@
       </c>
       <c r="C10" s="18" t="n"/>
       <c r="D10" s="19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>26</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.65</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>38</v>
@@ -12527,7 +12527,7 @@
         <v>25</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.6578947368421053</v>
@@ -12851,16 +12851,16 @@
       </c>
       <c r="C20" s="18" t="inlineStr"/>
       <c r="D20" s="19" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>69</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>0.5307692307692308</v>
+        <v>0.5390625</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>123</v>
@@ -12869,7 +12869,7 @@
         <v>71</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>0.9461538461538461</v>
+        <v>0.9609375</v>
       </c>
       <c r="K20" s="20" t="n">
         <v>0.5772357723577236</v>
@@ -19714,7 +19714,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
@@ -19723,7 +19723,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0.8</v>
@@ -19746,7 +19746,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
@@ -19755,7 +19755,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9230769230769231</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0.9166666666666666</v>

--- a/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,7 +89,7 @@
       <name val="阿里巴巴普惠体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -120,7 +120,14 @@
       <name val="阿里巴巴普惠体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="阿里巴巴普惠体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -326,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -375,7 +382,7 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="13" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -384,13 +391,16 @@
     <xf numFmtId="9" fontId="12" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="11" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="13" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,12 +869,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -884,17 +894,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -903,12 +913,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -922,17 +927,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -947,7 +952,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -962,7 +967,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -972,17 +977,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -991,16 +996,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1079,11 +1079,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1093,12 +1098,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1118,7 +1123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1133,7 +1138,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1143,17 +1148,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1162,11 +1167,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1176,12 +1186,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1201,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1226,17 +1236,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1245,12 +1255,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1264,17 +1269,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1314,17 +1319,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1333,7 +1338,12 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1347,12 +1357,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1372,7 +1382,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,7 +1397,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1397,17 +1407,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1420,7 +1430,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1430,12 +1440,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1455,7 +1465,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1470,7 +1480,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1480,17 +1490,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1499,16 +1509,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1518,12 +1523,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1543,7 +1548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1568,17 +1573,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1591,7 +1596,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1601,12 +1606,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1651,17 +1656,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1684,12 +1689,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1709,7 +1714,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1739,12 +1744,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1753,12 +1758,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1822,17 +1822,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1841,16 +1841,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1860,12 +1855,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1910,17 +1905,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1943,12 +1938,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1968,12 +1963,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1983,7 +1978,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1993,17 +1988,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2012,11 +2007,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2178,16 +2178,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>9,10,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2197,12 +2192,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2222,7 +2217,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2237,7 +2232,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2247,17 +2242,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2266,16 +2261,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2285,12 +2275,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2310,7 +2300,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2325,7 +2315,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2335,17 +2325,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2354,16 +2344,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2373,12 +2363,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2398,7 +2388,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2413,7 +2403,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2423,17 +2413,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2442,11 +2432,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2456,12 +2451,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2481,12 +2476,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2496,7 +2491,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2506,17 +2501,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2529,7 +2524,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2539,17 +2534,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2564,12 +2559,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2589,17 +2584,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2608,12 +2603,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2627,17 +2617,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2652,7 +2642,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2667,7 +2657,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2677,17 +2667,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2696,11 +2686,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2710,12 +2705,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2735,7 +2730,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2750,7 +2745,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2760,17 +2755,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2779,11 +2774,16 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2862,7 +2862,12 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2876,12 +2881,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2901,7 +2906,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2916,7 +2921,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2926,17 +2931,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2945,16 +2950,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3014,17 +3014,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3033,11 +3033,16 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3047,12 +3052,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3072,7 +3077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3087,7 +3092,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3097,17 +3102,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3125,7 +3130,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3135,12 +3140,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3160,7 +3165,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3175,7 +3180,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3185,17 +3190,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3204,11 +3209,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3218,12 +3228,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3243,12 +3253,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3258,7 +3268,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3268,17 +3278,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3287,16 +3297,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3306,17 +3311,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3331,7 +3336,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3346,7 +3351,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3356,17 +3361,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3375,11 +3380,16 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3389,12 +3399,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3414,12 +3424,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3429,7 +3439,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3439,17 +3449,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3458,16 +3468,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3477,17 +3482,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3502,12 +3507,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3527,17 +3532,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3546,7 +3551,12 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3560,17 +3570,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3585,7 +3595,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3600,7 +3610,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3610,17 +3620,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3638,7 +3648,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3648,12 +3658,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3673,12 +3683,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3688,7 +3698,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3698,17 +3708,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3717,11 +3727,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3731,17 +3746,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3756,7 +3771,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3786,12 +3801,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3800,12 +3815,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3819,12 +3829,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3844,12 +3854,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3859,7 +3869,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3869,17 +3879,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3892,7 +3902,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3902,17 +3912,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3927,7 +3937,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3942,7 +3952,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3952,17 +3962,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3975,7 +3985,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3985,12 +3995,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4010,7 +4020,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4025,7 +4035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4035,17 +4045,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4063,7 +4073,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4073,12 +4083,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4098,12 +4108,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4113,7 +4123,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4123,17 +4133,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4142,11 +4152,16 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4156,17 +4171,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4181,7 +4196,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4196,7 +4211,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4206,17 +4221,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4225,16 +4240,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4244,12 +4254,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4269,7 +4279,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4284,7 +4294,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4294,17 +4304,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4313,11 +4323,16 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4327,12 +4342,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4352,7 +4367,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4377,17 +4392,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4396,7 +4411,12 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -4410,12 +4430,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4435,7 +4455,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4450,7 +4470,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4460,17 +4480,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4479,11 +4499,16 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4493,12 +4518,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4518,7 +4543,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4548,12 +4573,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4562,7 +4587,12 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4576,12 +4606,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4601,7 +4631,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4626,17 +4656,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4664,12 +4694,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4689,12 +4719,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4714,17 +4744,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4733,12 +4763,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4752,17 +4777,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4777,7 +4802,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4792,7 +4817,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4802,17 +4827,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4821,16 +4846,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4840,12 +4860,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4865,7 +4885,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4880,7 +4900,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4890,17 +4910,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4909,11 +4929,16 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4923,12 +4948,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4948,7 +4973,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4963,7 +4988,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4973,17 +4998,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4992,16 +5017,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5011,12 +5036,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5036,7 +5061,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5051,7 +5076,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5061,17 +5086,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5080,11 +5105,16 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5094,12 +5124,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5119,12 +5149,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5134,7 +5164,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5144,17 +5174,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5167,7 +5197,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5177,17 +5207,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5202,7 +5232,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5232,12 +5262,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5246,7 +5276,12 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5260,12 +5295,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5285,7 +5320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5300,7 +5335,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5310,17 +5345,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5329,11 +5364,16 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5343,12 +5383,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5368,7 +5408,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5383,7 +5423,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5393,17 +5433,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5416,7 +5456,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5426,12 +5466,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5451,7 +5491,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5466,7 +5506,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5476,17 +5516,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5495,16 +5535,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5514,12 +5549,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5539,7 +5574,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5554,7 +5589,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5564,17 +5599,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5583,16 +5618,16 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>6,7,8,9,10</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5602,12 +5637,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5627,7 +5662,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5642,7 +5677,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5652,17 +5687,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5680,7 +5715,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5690,12 +5725,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5715,7 +5750,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5740,17 +5775,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5773,12 +5808,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5798,7 +5833,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5813,7 +5848,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5823,17 +5858,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5842,11 +5877,16 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5856,12 +5896,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5881,7 +5921,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5906,17 +5946,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5925,12 +5965,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5944,12 +5979,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5969,7 +6004,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5984,7 +6019,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5994,17 +6029,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6017,7 +6052,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6027,12 +6062,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6052,7 +6087,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6067,7 +6102,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6077,17 +6112,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6100,7 +6135,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6110,12 +6145,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6135,12 +6170,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6150,7 +6185,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6160,17 +6195,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6179,16 +6214,11 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>15,16,17,18,19,20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6198,17 +6228,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6223,7 +6253,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6253,12 +6283,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6281,12 +6311,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6306,7 +6336,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6321,7 +6351,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6331,17 +6361,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6359,7 +6389,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6369,12 +6399,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6394,7 +6424,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6409,7 +6439,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6419,17 +6449,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6438,16 +6468,11 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6457,12 +6482,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6482,7 +6507,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6497,7 +6522,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6507,17 +6532,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6530,7 +6555,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6540,12 +6565,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6565,7 +6590,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6580,7 +6605,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6590,17 +6615,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6618,7 +6643,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6628,12 +6653,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6653,7 +6678,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6668,7 +6693,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6678,17 +6703,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6701,7 +6726,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6711,12 +6736,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6736,7 +6761,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6751,7 +6776,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6761,17 +6786,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6780,11 +6805,16 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6794,12 +6824,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6819,7 +6849,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6834,7 +6864,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6844,17 +6874,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6872,7 +6902,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6882,12 +6912,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6907,7 +6937,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6922,7 +6952,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6932,17 +6962,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6955,7 +6985,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6965,12 +6995,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6990,7 +7020,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7015,17 +7045,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7034,12 +7064,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -7053,12 +7078,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7078,7 +7103,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7093,7 +7118,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7103,17 +7128,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7126,7 +7151,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7136,12 +7161,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7161,7 +7186,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7176,7 +7201,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7186,17 +7211,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7209,7 +7234,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7219,12 +7244,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7244,12 +7269,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7259,7 +7284,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7269,17 +7294,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7288,11 +7313,16 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7302,17 +7332,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7327,7 +7357,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7342,7 +7372,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7352,17 +7382,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7371,11 +7401,16 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7385,12 +7420,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7410,7 +7445,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7435,17 +7470,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7454,7 +7489,12 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -7468,12 +7508,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7493,7 +7533,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7508,7 +7548,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7518,17 +7558,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7537,16 +7577,11 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7556,12 +7591,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7581,7 +7616,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7611,12 +7646,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7625,12 +7660,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -7644,12 +7674,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7669,7 +7699,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7684,7 +7714,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7694,17 +7724,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7717,7 +7747,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -7727,12 +7757,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7752,7 +7782,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7767,7 +7797,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7777,17 +7807,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7796,16 +7826,11 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -7815,12 +7840,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7840,7 +7865,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7855,7 +7880,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7865,17 +7890,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7884,16 +7909,16 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -7903,12 +7928,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7928,7 +7953,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7943,7 +7968,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7953,17 +7978,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7981,7 +8006,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -7991,12 +8016,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -8016,7 +8041,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8046,12 +8071,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8060,12 +8085,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -8079,12 +8099,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -8104,7 +8124,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8119,7 +8139,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8129,17 +8149,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8148,11 +8168,16 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8162,12 +8187,12 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -8187,7 +8212,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -8202,7 +8227,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8212,17 +8237,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8235,7 +8260,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8245,12 +8270,12 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -8270,7 +8295,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8285,7 +8310,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8295,17 +8320,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8314,16 +8339,16 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8333,12 +8358,12 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -8358,7 +8383,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8383,17 +8408,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8402,7 +8427,12 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -8416,12 +8446,12 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8441,12 +8471,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8466,17 +8496,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8485,12 +8515,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -8504,17 +8529,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8529,7 +8554,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8554,17 +8579,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8587,12 +8612,12 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8612,7 +8637,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8637,17 +8662,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8670,12 +8695,12 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8695,7 +8720,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8710,7 +8735,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8720,17 +8745,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8739,11 +8764,16 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8753,12 +8783,12 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -8778,7 +8808,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8793,7 +8823,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8803,17 +8833,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8826,7 +8856,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -8836,12 +8866,12 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8861,7 +8891,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8876,7 +8906,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8886,17 +8916,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8909,7 +8939,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8919,12 +8949,12 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8944,7 +8974,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8959,7 +8989,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8969,17 +8999,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8992,7 +9022,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -9002,12 +9032,12 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -9027,7 +9057,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9042,7 +9072,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -9052,17 +9082,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9075,7 +9105,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9085,12 +9115,12 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -9110,7 +9140,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9125,68 +9155,151 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>继往开来-姜志强</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>zhongwenxuan01</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>仲文璇</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>zhongwenxuan01</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>仲文璇</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>高阶二</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>劲揽山河-刘劲松</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>wangrumeng</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>王如梦</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>破浪前行-陈嘉博</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>zhangjunmei</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>张军妹</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="K99" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>高二</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>wangrumeng</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>王如梦</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>zhangjunmei</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>张军妹</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
         <is>
           <t>高中</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -9255,13 +9368,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -9284,10 +9397,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -9310,10 +9423,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="5">
@@ -9362,10 +9475,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -9388,10 +9501,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -9414,10 +9527,10 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="9">
@@ -9466,10 +9579,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -9518,10 +9631,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -9544,10 +9657,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>
@@ -9580,7 +9693,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 10月8日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 10月9日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -9668,28 +9781,28 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.625</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G3" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="11" t="n">
         <v>8</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>7</v>
       </c>
       <c r="I3" s="11" t="n">
         <v>5</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K3" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -9704,10 +9817,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>8</v>
@@ -9716,13 +9829,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -9734,28 +9847,28 @@
       </c>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>15</v>
-      </c>
       <c r="I5" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="20" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>0.6875</v>
       </c>
     </row>
     <row r="6">
@@ -9774,10 +9887,10 @@
         <v>11</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>11</v>
@@ -9791,7 +9904,7 @@
       <c r="J6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>0.4545454545454545</v>
       </c>
     </row>
@@ -9809,7 +9922,7 @@
       <c r="E7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="23" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="G7" s="11" t="n">
@@ -9840,10 +9953,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0.875</v>
+        <v>6</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0.75</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>8</v>
@@ -9873,10 +9986,10 @@
         <v>26</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>26</v>
@@ -9890,7 +10003,7 @@
       <c r="J9" s="20" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="21" t="n">
         <v>0.68</v>
       </c>
     </row>
@@ -9910,10 +10023,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.75</v>
+        <v>4</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>4</v>
@@ -9943,10 +10056,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.2857142857142857</v>
+        <v>3</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.4285714285714285</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>7</v>
@@ -9960,7 +10073,7 @@
       <c r="J11" s="12" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9978,7 +10091,7 @@
       <c r="E12" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="G12" s="11" t="n">
@@ -9993,7 +10106,7 @@
       <c r="J12" s="12" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -10009,10 +10122,10 @@
         <v>20</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>0.4</v>
+        <v>10</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0.5</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>20</v>
@@ -10023,10 +10136,10 @@
       <c r="I13" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="18" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -10046,10 +10159,10 @@
         <v>10</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0.6</v>
+        <v>7</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0.7</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>10</v>
@@ -10081,7 +10194,7 @@
       <c r="E15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="G15" s="11" t="n">
@@ -10096,7 +10209,7 @@
       <c r="J15" s="12" t="n">
         <v>0.875</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="K15" s="22" t="n">
         <v>0.5714285714285714</v>
       </c>
     </row>
@@ -10112,10 +10225,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>0.5</v>
+        <v>4</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0.4</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>10</v>
@@ -10129,7 +10242,7 @@
       <c r="J16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="K16" s="22" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -10145,10 +10258,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>0.3333333333333333</v>
+        <v>5</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.5555555555555556</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>9</v>
@@ -10178,10 +10291,10 @@
         <v>37</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>0.4864864864864865</v>
+        <v>20</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.5405405405405406</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>37</v>
@@ -10195,7 +10308,7 @@
       <c r="J18" s="20" t="n">
         <v>0.9459459459459459</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="18" t="n">
         <v>0.5428571428571428</v>
       </c>
     </row>
@@ -10212,28 +10325,28 @@
       </c>
       <c r="C19" s="16" t="inlineStr"/>
       <c r="D19" s="17" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>0.5757575757575758</v>
+        <v>54</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0.54</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J19" s="20" t="n">
-        <v>0.9393939393939394</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>0.5851063829787234</v>
       </c>
     </row>
   </sheetData>
@@ -10349,7 +10462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10374,19 +10487,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -10400,7 +10513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10425,19 +10538,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -10451,7 +10564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10476,19 +10589,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -10502,7 +10615,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10527,12 +10640,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -10553,7 +10666,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10578,19 +10691,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10604,7 +10717,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10629,19 +10742,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -10655,7 +10768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10680,12 +10793,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -10706,7 +10819,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10731,19 +10844,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10757,7 +10870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10777,24 +10890,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -10808,7 +10921,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10833,19 +10946,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -10859,7 +10972,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10884,12 +10997,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -10910,7 +11023,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10935,19 +11048,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -10961,7 +11074,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10986,19 +11099,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -11012,7 +11125,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11037,12 +11150,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -11063,7 +11176,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11088,19 +11201,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -11114,7 +11227,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11139,19 +11252,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -11165,7 +11278,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11180,29 +11293,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -11216,7 +11329,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11241,12 +11354,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -11267,7 +11380,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11292,12 +11405,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -11318,7 +11431,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11343,19 +11456,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -11369,7 +11482,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11394,12 +11507,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -11420,7 +11533,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11445,12 +11558,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -11471,7 +11584,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11496,12 +11609,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -11522,7 +11635,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11547,19 +11660,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -11573,7 +11686,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11598,12 +11711,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -11624,7 +11737,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11649,12 +11762,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -11675,7 +11788,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11700,19 +11813,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -11726,7 +11839,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11746,17 +11859,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -11777,7 +11890,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11802,12 +11915,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -11828,7 +11941,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11853,12 +11966,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -11879,7 +11992,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11904,12 +12017,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -11930,7 +12043,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11955,19 +12068,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11981,7 +12094,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12006,19 +12119,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -12032,7 +12145,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12052,17 +12165,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -12083,7 +12196,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12108,19 +12221,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -12134,7 +12247,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12159,19 +12272,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -12185,7 +12298,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12210,12 +12323,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -12236,7 +12349,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12261,12 +12374,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -12287,7 +12400,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12312,12 +12425,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -12338,7 +12451,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12363,12 +12476,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -12389,7 +12502,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12414,12 +12527,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -12440,7 +12553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12455,22 +12568,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -12491,7 +12604,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12516,12 +12629,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -12542,7 +12655,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12567,12 +12680,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -12593,7 +12706,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12618,19 +12731,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -12644,7 +12757,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12664,21 +12777,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -12695,7 +12808,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12720,19 +12833,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -12746,7 +12859,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12771,19 +12884,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -12797,7 +12910,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12822,19 +12935,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12848,7 +12961,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12873,19 +12986,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="H51" t="n">
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12899,7 +13012,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12924,12 +13037,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -12950,7 +13063,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12975,19 +13088,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -13001,7 +13114,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13021,17 +13134,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -13052,7 +13165,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -13077,19 +13190,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -13103,7 +13216,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -13128,12 +13241,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -13154,7 +13267,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13179,12 +13292,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -13205,7 +13318,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13230,12 +13343,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -13256,7 +13369,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13281,19 +13394,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -13307,7 +13420,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13332,19 +13445,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -13358,7 +13471,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13383,16 +13496,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -13409,7 +13522,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13434,12 +13547,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -13460,7 +13573,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13475,29 +13588,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -13511,7 +13624,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13536,12 +13649,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -13562,7 +13675,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13587,12 +13700,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -13613,7 +13726,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13638,19 +13751,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -13664,7 +13777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13689,19 +13802,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -13715,7 +13828,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13740,12 +13853,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -13766,7 +13879,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13791,19 +13904,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -13817,7 +13930,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13842,19 +13955,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -13868,7 +13981,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13893,19 +14006,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -13919,7 +14032,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13944,19 +14057,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -13970,7 +14083,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13990,24 +14103,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -14021,7 +14134,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14046,19 +14159,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14072,7 +14185,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14097,12 +14210,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -14123,7 +14236,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14148,19 +14261,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14174,7 +14287,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -14225,7 +14338,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -14276,7 +14389,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -14327,7 +14440,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14378,7 +14491,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14429,7 +14542,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14480,7 +14593,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14531,7 +14644,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14582,7 +14695,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14633,7 +14746,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -14684,7 +14797,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -14735,7 +14848,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -14786,7 +14899,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -14837,7 +14950,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -14888,7 +15001,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -14939,7 +15052,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14990,7 +15103,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -15041,7 +15154,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15092,7 +15205,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -15143,7 +15256,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15194,7 +15307,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15245,7 +15358,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15296,7 +15409,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15417,19 +15530,19 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="3">
@@ -15455,13 +15568,13 @@
         <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
